--- a/product_selector_out/STM32L4x3.xlsx
+++ b/product_selector_out/STM32L4x3.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX19" s="4" t="inlineStr">
@@ -4439,9 +4439,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="8" t="inlineStr">
@@ -4766,9 +4766,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="8" t="inlineStr">
@@ -5093,9 +5093,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="8" t="inlineStr">
@@ -5420,9 +5420,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="8" t="inlineStr">
@@ -5747,9 +5747,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="8" t="inlineStr">
@@ -6074,9 +6074,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="8" t="inlineStr">
@@ -6401,9 +6401,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="8" t="inlineStr">
@@ -6728,9 +6728,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="8" t="inlineStr">
@@ -6829,7 +6829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6922,19 +6922,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L443RC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6988,19 +6988,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7010,19 +7010,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7054,19 +7054,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7076,19 +7076,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7098,14 +7098,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7127,7 +7127,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7142,14 +7142,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7171,12 +7171,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7186,19 +7186,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7208,19 +7208,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7230,19 +7230,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7252,19 +7252,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7274,19 +7274,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7296,19 +7296,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7318,19 +7318,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7340,19 +7340,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7362,27 +7362,203 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>STM32L443CC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32L433CC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>STM32L433RC</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32L433RC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>Operating Temperature (°C) max</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32L4x3.xlsx
+++ b/product_selector_out/STM32L4x3.xlsx
@@ -1085,7 +1085,7 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>10, 11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>15, 16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
@@ -4299,14 +4299,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
@@ -4329,9 +4329,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="6" t="inlineStr">
@@ -4626,14 +4626,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
@@ -4656,9 +4656,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -4953,14 +4953,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
@@ -4983,9 +4983,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -5280,14 +5280,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U15" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
@@ -5310,9 +5310,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -5607,14 +5607,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
@@ -5637,9 +5637,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="6" t="inlineStr">
@@ -5934,14 +5934,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -5964,9 +5964,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -6261,14 +6261,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
@@ -6291,9 +6291,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="6" t="inlineStr">
@@ -6588,14 +6588,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
@@ -6618,9 +6618,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="6" t="inlineStr">

--- a/product_selector_out/STM32L4x3.xlsx
+++ b/product_selector_out/STM32L4x3.xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AM12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN12" s="4" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AM13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN13" s="4" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AM14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN14" s="4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AM15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN15" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AM16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN16" s="4" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AM17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN17" s="4" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AM18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN18" s="4" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="AM19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN19" s="4" t="inlineStr">
@@ -4389,9 +4389,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr">
@@ -4716,9 +4716,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -5043,9 +5043,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -5370,9 +5370,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -5697,9 +5697,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr">
@@ -6024,9 +6024,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">
@@ -6351,9 +6351,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -6678,9 +6678,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">

--- a/product_selector_out/STM32L4x3.xlsx
+++ b/product_selector_out/STM32L4x3.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.3828125" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l443cc.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l443cc.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l443cc.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
@@ -3609,12 +3651,17 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -3635,16 +3682,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -3657,6 +3702,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -3676,7 +3722,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -3701,7 +3749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3769,6 +3817,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4102,6 +4151,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -4197,6 +4251,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4519,7 +4574,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4846,7 +4906,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5173,7 +5238,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5500,7 +5570,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5827,7 +5902,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6154,7 +6234,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6481,7 +6566,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6808,7 +6898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6816,8 +6911,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
